--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414933</v>
       </c>
       <c r="B2" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414934</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414933</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414934</v>
       </c>
       <c r="B3" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414933</v>
       </c>
       <c r="B2" t="n">
-        <v>79563</v>
+        <v>79566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414934</v>
       </c>
       <c r="B3" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414933</v>
       </c>
       <c r="B2" t="n">
-        <v>79566</v>
+        <v>79572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414934</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -678,29 +678,29 @@
         <v>127414933</v>
       </c>
       <c r="B2" t="n">
-        <v>79572</v>
+        <v>78839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>125</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk lundlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scutula effusa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Rabenh.) Kistenich et al.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,6 +708,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ejheden, Dlr</t>
@@ -763,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414933</v>
       </c>
       <c r="B2" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414933</v>
       </c>
       <c r="B2" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414933</v>
       </c>
       <c r="B2" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414933</v>
       </c>
       <c r="B2" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414933</v>
       </c>
       <c r="B2" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414933</v>
       </c>
       <c r="B2" t="n">
-        <v>78938</v>
+        <v>78853</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127414933</v>
+        <v>127414934</v>
       </c>
       <c r="B2" t="n">
-        <v>78938</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,19 +708,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ejheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504932</v>
+        <v>504744</v>
       </c>
       <c r="R2" t="n">
-        <v>6806537</v>
+        <v>6806702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +763,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127414934</v>
+        <v>127414933</v>
       </c>
       <c r="B3" t="n">
-        <v>78787</v>
+        <v>79085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -818,16 +814,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ejheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504744</v>
+        <v>504932</v>
       </c>
       <c r="R3" t="n">
-        <v>6806702</v>
+        <v>6806537</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34241-2025 artfynd.xlsx
+++ b/artfynd/A 34241-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414934</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,8 +898,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414933</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>